--- a/artifacts/layer-analysis-example.xlsx
+++ b/artifacts/layer-analysis-example.xlsx
@@ -79,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -99,6 +99,20 @@
       </top>
       <bottom style="thin">
         <color rgb="0041484D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0041484D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0041484D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0041484D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFCC00"/>
       </bottom>
     </border>
   </borders>
@@ -122,7 +136,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,6 +242,7 @@
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>T1053  Scheduled Task/Job
+T1053  Scheduled Task/Job
 Score: 60
 Aggregate: 180
 Selected: True
@@ -237,6 +252,7 @@
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <t>T1053  Scheduled Task/Job
+T1053  Scheduled Task/Job
 Score: 60
 Aggregate: 160
 Selected: True
@@ -246,6 +262,7 @@
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <t>T1053  Scheduled Task/Job
+T1053  Scheduled Task/Job
 Score: 60
 Aggregate: 160
 Selected: True
@@ -254,7 +271,8 @@
     </comment>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.002  At
+        <t>T1053.002  At
+&gt; T1053.002  At
 Score: 0
 Selected: True
 Enabled: True</t>
@@ -262,7 +280,8 @@
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.002  At
+        <t>T1053.002  At
+&gt; T1053.002  At
 Score: 0
 Selected: True
 Enabled: True</t>
@@ -270,7 +289,8 @@
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.002  At
+        <t>T1053.002  At
+&gt; T1053.002  At
 Score: 0
 Selected: True
 Enabled: True</t>
@@ -278,17 +298,20 @@
     </comment>
     <comment ref="A6" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.005  Scheduled Task
+        <t>T1053.005  Scheduled Task
+&gt; T1053.005  Scheduled Task
 Score: 120
 Selected: True
 Enabled: True
+Annotation indicators: #ffcc00
 =SUM(1,2)
 中文 &lt;tag&gt; &amp; details</t>
       </text>
     </comment>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.005  Scheduled Task
+        <t>T1053.005  Scheduled Task
+&gt; T1053.005  Scheduled Task
 Score: 100
 Selected: True
 Enabled: True</t>
@@ -296,7 +319,8 @@
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1053.005  Scheduled Task
+        <t>T1053.005  Scheduled Task
+&gt; T1053.005  Scheduled Task
 Score: 100
 Selected: True
 Enabled: True</t>
@@ -613,24 +637,24 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Enterprise v19.2 · Windows</t>
+          <t>Enterprise v20.0 · Windows</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>TA0002  Execution</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>TA0003  Persistence</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Privilege Escalation</t>
+          <t>TA0004  Privilege Escalation</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1301,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Enterprise v19.2</t>
+          <t>Enterprise v20.0</t>
         </is>
       </c>
     </row>
@@ -1408,70 +1432,94 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Missing scores</t>
+          <t>Calculation mode</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>zero</t>
+          <t>studio</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Source a</t>
+          <t>Missing scores</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Assessment A (b725c125-f2e2-4d48-9f63-7c8c83687513)</t>
+          <t>zero</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Source b</t>
+          <t>Calculation scope</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Assessment B (d40ada60-97ab-4aa7-bf05-a08797b5726f)</t>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Legend: Gradient 0–200: #ff6666</t>
+          <t>Source a</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>#ff6666</t>
+          <t>Assessment A (2e999442-d98b-480c-91da-9b1a11b376f1)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Legend: Gradient 0–200: #ffe766</t>
+          <t>Source b</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>#ffe766</t>
+          <t>Assessment B (e4fe8b84-59ac-43bf-acac-4f14dc88ddc5)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>Legend: Gradient 0–200: #ff6666</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>#ff6666</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Legend: Gradient 0–200: #ffe766</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>#ffe766</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>Legend: Gradient 0–200: #8ec843</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>#8ec843</t>
         </is>
